--- a/Daily_Report/Top 7 broker List with its Turnover 2024-11-12.xlsx
+++ b/Daily_Report/Top 7 broker List with its Turnover 2024-11-12.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="270">
   <si>
     <t>Date: 2024-11-12</t>
   </si>
@@ -101,67 +101,67 @@
     <t>42</t>
   </si>
   <si>
-    <t>795,611,610.85</t>
-  </si>
-  <si>
-    <t>724,988,158.2</t>
-  </si>
-  <si>
-    <t>639,702,428.09</t>
-  </si>
-  <si>
-    <t>533,772,828.59</t>
-  </si>
-  <si>
-    <t>508,688,076.75</t>
-  </si>
-  <si>
-    <t>488,725,609.65</t>
-  </si>
-  <si>
-    <t>454,591,607.2</t>
-  </si>
-  <si>
-    <t>339,633,271.16</t>
-  </si>
-  <si>
-    <t>370,688,020.1</t>
-  </si>
-  <si>
-    <t>296,370,448.7</t>
-  </si>
-  <si>
-    <t>275,430,846.5</t>
-  </si>
-  <si>
-    <t>236,011,873.35</t>
-  </si>
-  <si>
-    <t>236,563,113.8</t>
-  </si>
-  <si>
-    <t>201,322,491.6</t>
-  </si>
-  <si>
-    <t>455,978,339.69</t>
-  </si>
-  <si>
-    <t>354,300,138.1</t>
-  </si>
-  <si>
-    <t>343,331,979.39</t>
-  </si>
-  <si>
-    <t>258,341,982.09</t>
-  </si>
-  <si>
-    <t>272,676,203.39</t>
-  </si>
-  <si>
-    <t>252,162,495.85</t>
-  </si>
-  <si>
-    <t>253,269,115.6</t>
+    <t>793,422,580.65</t>
+  </si>
+  <si>
+    <t>724,661,021.9</t>
+  </si>
+  <si>
+    <t>642,350,683.0</t>
+  </si>
+  <si>
+    <t>533,165,350.99</t>
+  </si>
+  <si>
+    <t>515,664,970.25</t>
+  </si>
+  <si>
+    <t>489,514,436.35</t>
+  </si>
+  <si>
+    <t>453,884,248.6</t>
+  </si>
+  <si>
+    <t>335,662,418.16</t>
+  </si>
+  <si>
+    <t>370,479,137.1</t>
+  </si>
+  <si>
+    <t>296,637,884.7</t>
+  </si>
+  <si>
+    <t>276,696,318.5</t>
+  </si>
+  <si>
+    <t>242,682,719.75</t>
+  </si>
+  <si>
+    <t>237,227,688.1</t>
+  </si>
+  <si>
+    <t>200,814,095.6</t>
+  </si>
+  <si>
+    <t>457,760,162.49</t>
+  </si>
+  <si>
+    <t>354,181,884.8</t>
+  </si>
+  <si>
+    <t>345,712,798.3</t>
+  </si>
+  <si>
+    <t>256,469,032.49</t>
+  </si>
+  <si>
+    <t>272,982,250.5</t>
+  </si>
+  <si>
+    <t>252,286,748.25</t>
+  </si>
+  <si>
+    <t>253,070,153.0</t>
   </si>
   <si>
     <t>Top 5 Buy</t>
@@ -179,16 +179,10 @@
     <t>% of turnover</t>
   </si>
   <si>
-    <t>MLBL</t>
-  </si>
-  <si>
-    <t>13,366,623.8</t>
-  </si>
-  <si>
     <t>GFCL</t>
   </si>
   <si>
-    <t>11,296,553.3</t>
+    <t>11,799,469.7</t>
   </si>
   <si>
     <t>AKJCL</t>
@@ -206,13 +200,19 @@
     <t>SHIVM</t>
   </si>
   <si>
-    <t>10,251,532.4</t>
+    <t>10,220,132.4</t>
+  </si>
+  <si>
+    <t>UMRH</t>
+  </si>
+  <si>
+    <t>10,189,457.8</t>
   </si>
   <si>
     <t>LSL</t>
   </si>
   <si>
-    <t>84,471,740.4</t>
+    <t>84,465,411.59</t>
   </si>
   <si>
     <t>SHPC</t>
@@ -227,7 +227,7 @@
     <t>9,739,405.6</t>
   </si>
   <si>
-    <t>9,559,816.9</t>
+    <t>9,538,156.9</t>
   </si>
   <si>
     <t>SICL</t>
@@ -245,7 +245,7 @@
     <t>JFL</t>
   </si>
   <si>
-    <t>43,073,786.9</t>
+    <t>43,159,959.0</t>
   </si>
   <si>
     <t>35,473,938.4</t>
@@ -260,10 +260,10 @@
     <t>13,533,777.2</t>
   </si>
   <si>
-    <t>12,184,791.5</t>
-  </si>
-  <si>
-    <t>11,510,748.9</t>
+    <t>12,401,091.5</t>
+  </si>
+  <si>
+    <t>11,589,928.9</t>
   </si>
   <si>
     <t>SAHAS</t>
@@ -272,7 +272,7 @@
     <t>9,871,415.1</t>
   </si>
   <si>
-    <t>5,655,910.0</t>
+    <t>5,664,710.0</t>
   </si>
   <si>
     <t>NLIC</t>
@@ -284,10 +284,16 @@
     <t>26,610,352.8</t>
   </si>
   <si>
+    <t>SCB</t>
+  </si>
+  <si>
+    <t>11,617,446.0</t>
+  </si>
+  <si>
     <t>HRL</t>
   </si>
   <si>
-    <t>8,235,419.9</t>
+    <t>8,327,219.9</t>
   </si>
   <si>
     <t>PFL</t>
@@ -299,16 +305,13 @@
     <t>6,444,142.8</t>
   </si>
   <si>
-    <t>6,267,269.1</t>
-  </si>
-  <si>
     <t>19,211,942.5</t>
   </si>
   <si>
-    <t>13,095,826.0</t>
-  </si>
-  <si>
-    <t>9,296,459.8</t>
+    <t>13,363,351.0</t>
+  </si>
+  <si>
+    <t>9,280,893.4</t>
   </si>
   <si>
     <t>6,259,596.0</t>
@@ -335,7 +338,10 @@
     <t>5,834,889.0</t>
   </si>
   <si>
-    <t>5,049,620.0</t>
+    <t>NFS</t>
+  </si>
+  <si>
+    <t>4,606,052.59</t>
   </si>
   <si>
     <t>Sell Amount</t>
@@ -344,7 +350,7 @@
     <t>NTC</t>
   </si>
   <si>
-    <t>48,892,850.0</t>
+    <t>51,922,950.0</t>
   </si>
   <si>
     <t>43,383,295.9</t>
@@ -368,7 +374,7 @@
     <t>61,792,282.7</t>
   </si>
   <si>
-    <t>29,848,863.3</t>
+    <t>30,254,921.1</t>
   </si>
   <si>
     <t>17,345,693.5</t>
@@ -380,10 +386,10 @@
     <t>11,291,246.5</t>
   </si>
   <si>
-    <t>9,807,650.3</t>
-  </si>
-  <si>
-    <t>148,514,755.0</t>
+    <t>9,710,383.1</t>
+  </si>
+  <si>
+    <t>149,578,101.4</t>
   </si>
   <si>
     <t>33,926,739.1</t>
@@ -392,16 +398,16 @@
     <t>HURJA</t>
   </si>
   <si>
-    <t>19,140,197.8</t>
-  </si>
-  <si>
-    <t>10,251,277.0</t>
+    <t>20,048,907.8</t>
+  </si>
+  <si>
+    <t>10,272,897.0</t>
   </si>
   <si>
     <t>6,803,825.4</t>
   </si>
   <si>
-    <t>16,023,158.5</t>
+    <t>13,622,928.5</t>
   </si>
   <si>
     <t>13,352,873.5</t>
@@ -416,10 +422,7 @@
     <t>11,492,909.4</t>
   </si>
   <si>
-    <t>RLFL</t>
-  </si>
-  <si>
-    <t>7,222,430.6</t>
+    <t>7,707,563.5</t>
   </si>
   <si>
     <t>28,206,515.0</t>
@@ -431,7 +434,7 @@
     <t>25,208,850.4</t>
   </si>
   <si>
-    <t>13,947,915.7</t>
+    <t>13,507,927.7</t>
   </si>
   <si>
     <t>SPC</t>
@@ -440,10 +443,10 @@
     <t>8,077,574.7</t>
   </si>
   <si>
-    <t>7,664,455.3</t>
-  </si>
-  <si>
-    <t>13,483,819.5</t>
+    <t>7,670,045.3</t>
+  </si>
+  <si>
+    <t>13,401,214.5</t>
   </si>
   <si>
     <t>SRLI</t>
@@ -470,7 +473,7 @@
     <t>13,665,873.0</t>
   </si>
   <si>
-    <t>13,424,176.4</t>
+    <t>13,077,176.4</t>
   </si>
   <si>
     <t>DHPL</t>
@@ -500,103 +503,103 @@
     <t>Percentage (%)</t>
   </si>
   <si>
-    <t>296,707,114.2</t>
-  </si>
-  <si>
-    <t>291,744,287.5</t>
-  </si>
-  <si>
-    <t>255,653,371.0</t>
-  </si>
-  <si>
-    <t>207,140,096.0</t>
-  </si>
-  <si>
-    <t>193,154,655.7</t>
+    <t>292,861,206.8</t>
+  </si>
+  <si>
+    <t>292,569,400.2</t>
+  </si>
+  <si>
+    <t>255,947,775.6</t>
+  </si>
+  <si>
+    <t>205,903,508.1</t>
+  </si>
+  <si>
+    <t>193,353,736.1</t>
   </si>
   <si>
     <t>Hydro Power</t>
   </si>
   <si>
-    <t>2,107,540,848.6</t>
+    <t>2,108,628,971.2</t>
   </si>
   <si>
     <t>Promoter Shares/debenture</t>
   </si>
   <si>
-    <t>1,663,913,843.5</t>
+    <t>1,659,267,349.3</t>
   </si>
   <si>
     <t>Finance</t>
   </si>
   <si>
-    <t>1,625,894,107.5</t>
+    <t>1,624,707,417.4</t>
   </si>
   <si>
     <t>Microfinance</t>
   </si>
   <si>
-    <t>586,671,562.1</t>
+    <t>590,944,128.6</t>
   </si>
   <si>
     <t>Development Banks</t>
   </si>
   <si>
-    <t>500,024,829.9</t>
+    <t>496,089,982.1</t>
   </si>
   <si>
     <t>Commercial Banks</t>
   </si>
   <si>
-    <t>432,538,771.0</t>
+    <t>439,612,725.0</t>
   </si>
   <si>
     <t>Investment</t>
   </si>
   <si>
-    <t>257,751,771.3</t>
+    <t>258,925,982.8</t>
   </si>
   <si>
     <t>Non Life Insurance</t>
   </si>
   <si>
-    <t>194,556,485.8</t>
+    <t>193,118,238.3</t>
   </si>
   <si>
     <t>Manufacturing And Processing</t>
   </si>
   <si>
-    <t>142,068,256.19</t>
+    <t>144,837,876.19</t>
   </si>
   <si>
     <t>Life Insurance</t>
   </si>
   <si>
-    <t>135,167,995.8</t>
+    <t>133,875,931.4</t>
   </si>
   <si>
     <t>Others</t>
   </si>
   <si>
-    <t>96,177,923.3</t>
+    <t>99,195,973.3</t>
   </si>
   <si>
     <t>Hotels And Tourism</t>
   </si>
   <si>
-    <t>86,856,762.6</t>
+    <t>85,844,456.9</t>
   </si>
   <si>
     <t>Trading</t>
   </si>
   <si>
-    <t>11,655,487.1</t>
+    <t>11,775,487.1</t>
   </si>
   <si>
     <t>Mutual Fund</t>
   </si>
   <si>
-    <t>10,960,746.91</t>
+    <t>10,508,083.91</t>
   </si>
   <si>
     <t>Tradings</t>
@@ -614,214 +617,214 @@
     <t>100%</t>
   </si>
   <si>
-    <t>122,405,057.5</t>
-  </si>
-  <si>
-    <t>65,787,281.8</t>
-  </si>
-  <si>
-    <t>46,701,683.2</t>
-  </si>
-  <si>
-    <t>29,400,503.7</t>
-  </si>
-  <si>
-    <t>15,958,930.4</t>
-  </si>
-  <si>
-    <t>133,434,458.4</t>
-  </si>
-  <si>
-    <t>101,029,714.1</t>
-  </si>
-  <si>
-    <t>54,101,322.7</t>
-  </si>
-  <si>
-    <t>17,251,009.8</t>
+    <t>122,737,890.0</t>
+  </si>
+  <si>
+    <t>65,631,056.8</t>
+  </si>
+  <si>
+    <t>46,724,323.6</t>
+  </si>
+  <si>
+    <t>25,193,780.8</t>
+  </si>
+  <si>
+    <t>16,038,960.4</t>
+  </si>
+  <si>
+    <t>133,340,959.6</t>
+  </si>
+  <si>
+    <t>100,992,529.1</t>
+  </si>
+  <si>
+    <t>53,510,248.5</t>
+  </si>
+  <si>
+    <t>17,521,514.8</t>
   </si>
   <si>
     <t>17,209,428.7</t>
   </si>
   <si>
-    <t>169,897,395.3</t>
+    <t>169,990,527.4</t>
   </si>
   <si>
     <t>51,328,513.4</t>
   </si>
   <si>
-    <t>28,479,396.1</t>
+    <t>28,884,530.0</t>
   </si>
   <si>
     <t>13,841,329.7</t>
   </si>
   <si>
-    <t>10,629,146.8</t>
-  </si>
-  <si>
-    <t>84,252,140.5</t>
-  </si>
-  <si>
-    <t>54,487,333.4</t>
-  </si>
-  <si>
-    <t>47,700,881.9</t>
-  </si>
-  <si>
-    <t>20,064,058.7</t>
-  </si>
-  <si>
-    <t>18,294,697.3</t>
-  </si>
-  <si>
-    <t>62,574,671.3</t>
-  </si>
-  <si>
-    <t>60,878,458.1</t>
-  </si>
-  <si>
-    <t>43,809,184.4</t>
-  </si>
-  <si>
-    <t>16,469,112.3</t>
-  </si>
-  <si>
-    <t>15,692,504.0</t>
-  </si>
-  <si>
-    <t>71,890,214.2</t>
-  </si>
-  <si>
-    <t>56,171,061.5</t>
-  </si>
-  <si>
-    <t>43,576,095.2</t>
-  </si>
-  <si>
-    <t>14,073,030.6</t>
-  </si>
-  <si>
-    <t>14,012,049.4</t>
-  </si>
-  <si>
-    <t>49,736,868.2</t>
-  </si>
-  <si>
-    <t>49,038,566.6</t>
-  </si>
-  <si>
-    <t>42,121,653.0</t>
-  </si>
-  <si>
-    <t>15,450,240.0</t>
-  </si>
-  <si>
-    <t>14,000,404.8</t>
-  </si>
-  <si>
-    <t>116,599,838.6</t>
-  </si>
-  <si>
-    <t>109,963,344.6</t>
-  </si>
-  <si>
-    <t>70,336,585.8</t>
-  </si>
-  <si>
-    <t>49,409,418.4</t>
-  </si>
-  <si>
-    <t>29,559,095.0</t>
-  </si>
-  <si>
-    <t>115,194,357.8</t>
-  </si>
-  <si>
-    <t>91,562,886.2</t>
-  </si>
-  <si>
-    <t>74,368,467.7</t>
-  </si>
-  <si>
-    <t>18,819,879.0</t>
-  </si>
-  <si>
-    <t>17,156,044.8</t>
-  </si>
-  <si>
-    <t>210,138,465.8</t>
-  </si>
-  <si>
-    <t>64,665,640.6</t>
-  </si>
-  <si>
-    <t>25,518,817.7</t>
+    <t>10,701,136.8</t>
+  </si>
+  <si>
+    <t>84,958,667.0</t>
+  </si>
+  <si>
+    <t>54,511,642.4</t>
+  </si>
+  <si>
+    <t>47,564,861.9</t>
+  </si>
+  <si>
+    <t>21,191,062.89</t>
+  </si>
+  <si>
+    <t>18,290,700.3</t>
+  </si>
+  <si>
+    <t>62,598,443.3</t>
+  </si>
+  <si>
+    <t>61,155,256.1</t>
+  </si>
+  <si>
+    <t>43,919,154.4</t>
+  </si>
+  <si>
+    <t>22,768,184.3</t>
+  </si>
+  <si>
+    <t>15,676,598.4</t>
+  </si>
+  <si>
+    <t>71,843,271.9</t>
+  </si>
+  <si>
+    <t>56,146,371.5</t>
+  </si>
+  <si>
+    <t>44,203,460.2</t>
+  </si>
+  <si>
+    <t>14,225,532.0</t>
+  </si>
+  <si>
+    <t>14,048,250.6</t>
+  </si>
+  <si>
+    <t>49,438,838.2</t>
+  </si>
+  <si>
+    <t>47,751,814.6</t>
+  </si>
+  <si>
+    <t>43,333,703.0</t>
+  </si>
+  <si>
+    <t>15,879,106.0</t>
+  </si>
+  <si>
+    <t>13,985,274.8</t>
+  </si>
+  <si>
+    <t>115,261,533.6</t>
+  </si>
+  <si>
+    <t>109,730,599.6</t>
+  </si>
+  <si>
+    <t>70,186,681.8</t>
+  </si>
+  <si>
+    <t>52,439,518.4</t>
+  </si>
+  <si>
+    <t>29,542,770.0</t>
+  </si>
+  <si>
+    <t>115,244,875.8</t>
+  </si>
+  <si>
+    <t>91,758,561.9</t>
+  </si>
+  <si>
+    <t>72,546,191.7</t>
+  </si>
+  <si>
+    <t>18,849,329.0</t>
+  </si>
+  <si>
+    <t>17,146,022.8</t>
+  </si>
+  <si>
+    <t>211,836,457.7</t>
+  </si>
+  <si>
+    <t>65,440,812.6</t>
+  </si>
+  <si>
+    <t>25,523,487.7</t>
   </si>
   <si>
     <t>11,373,941.4</t>
   </si>
   <si>
-    <t>10,858,065.9</t>
-  </si>
-  <si>
-    <t>68,768,023.5</t>
-  </si>
-  <si>
-    <t>65,223,349.9</t>
-  </si>
-  <si>
-    <t>43,202,514.4</t>
-  </si>
-  <si>
-    <t>29,648,821.0</t>
-  </si>
-  <si>
-    <t>18,273,067.7</t>
-  </si>
-  <si>
-    <t>107,879,856.5</t>
-  </si>
-  <si>
-    <t>65,071,996.7</t>
-  </si>
-  <si>
-    <t>43,193,862.9</t>
-  </si>
-  <si>
-    <t>15,642,509.3</t>
+    <t>10,841,644.9</t>
+  </si>
+  <si>
+    <t>66,855,827.1</t>
+  </si>
+  <si>
+    <t>64,863,028.9</t>
+  </si>
+  <si>
+    <t>43,201,737.8</t>
+  </si>
+  <si>
+    <t>29,630,866.0</t>
+  </si>
+  <si>
+    <t>18,277,705.7</t>
+  </si>
+  <si>
+    <t>107,949,220.5</t>
+  </si>
+  <si>
+    <t>65,261,294.7</t>
+  </si>
+  <si>
+    <t>42,753,874.9</t>
+  </si>
+  <si>
+    <t>15,867,511.7</t>
   </si>
   <si>
     <t>13,984,626.3</t>
   </si>
   <si>
-    <t>67,590,843.5</t>
-  </si>
-  <si>
-    <t>60,678,731.0</t>
-  </si>
-  <si>
-    <t>55,344,285.3</t>
-  </si>
-  <si>
-    <t>16,428,238.7</t>
+    <t>67,526,078.5</t>
+  </si>
+  <si>
+    <t>60,687,968.4</t>
+  </si>
+  <si>
+    <t>55,335,285.3</t>
+  </si>
+  <si>
+    <t>16,729,988.7</t>
   </si>
   <si>
     <t>12,971,798.7</t>
   </si>
   <si>
-    <t>70,824,817.2</t>
-  </si>
-  <si>
-    <t>61,519,239.8</t>
-  </si>
-  <si>
-    <t>53,774,845.1</t>
+    <t>70,736,628.59</t>
+  </si>
+  <si>
+    <t>61,647,981.8</t>
+  </si>
+  <si>
+    <t>53,446,477.1</t>
   </si>
   <si>
     <t>18,623,785.0</t>
   </si>
   <si>
-    <t>8,887,344.69</t>
+    <t>9,077,184.69</t>
   </si>
 </sst>
 </file>
@@ -1630,7 +1633,7 @@
         <v>55</v>
       </c>
       <c r="D9" s="10">
-        <v>0.01680043832658453</v>
+        <v>0.01487160812884031</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>64</v>
@@ -1639,7 +1642,7 @@
         <v>65</v>
       </c>
       <c r="G9" s="12">
-        <v>0.1165146484733301</v>
+        <v>0.1165585136323999</v>
       </c>
       <c r="H9" s="13" t="s">
         <v>73</v>
@@ -1648,16 +1651,16 @@
         <v>74</v>
       </c>
       <c r="J9" s="14">
-        <v>0.1044440609651017</v>
+        <v>0.1040134636238878</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="L9" s="15" t="s">
         <v>81</v>
       </c>
       <c r="M9" s="16">
-        <v>0.02282767283637689</v>
+        <v>0.02325937249480526</v>
       </c>
       <c r="N9" s="17" t="s">
         <v>68</v>
@@ -1666,25 +1669,25 @@
         <v>88</v>
       </c>
       <c r="P9" s="18">
-        <v>0.05231172896760844</v>
+        <v>0.05160395670681103</v>
       </c>
       <c r="Q9" s="15" t="s">
         <v>64</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S9" s="16">
-        <v>0.0393102839725518</v>
+        <v>0.03924693752292848</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="V9" s="18">
-        <v>0.02439487162621774</v>
+        <v>0.02443288995863162</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1696,7 +1699,7 @@
         <v>57</v>
       </c>
       <c r="D10" s="10">
-        <v>0.01419857773057285</v>
+        <v>0.01345448624773772</v>
       </c>
       <c r="E10" s="11" t="s">
         <v>66</v>
@@ -1705,7 +1708,7 @@
         <v>67</v>
       </c>
       <c r="G10" s="12">
-        <v>0.03992705821825931</v>
+        <v>0.03994508263202061</v>
       </c>
       <c r="H10" s="13" t="s">
         <v>75</v>
@@ -1714,16 +1717,16 @@
         <v>76</v>
       </c>
       <c r="J10" s="14">
-        <v>0.06733409943109767</v>
+        <v>0.06719064856976263</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="L10" s="15" t="s">
         <v>82</v>
       </c>
       <c r="M10" s="16">
-        <v>0.0215648835674279</v>
+        <v>0.02173796342631684</v>
       </c>
       <c r="N10" s="17" t="s">
         <v>89</v>
@@ -1732,25 +1735,25 @@
         <v>90</v>
       </c>
       <c r="P10" s="18">
-        <v>0.01618952807507494</v>
+        <v>0.02252905795475643</v>
       </c>
       <c r="Q10" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="R10" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="S10" s="16">
+        <v>0.02729919693409262</v>
+      </c>
+      <c r="T10" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="R10" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="S10" s="16">
-        <v>0.02679586610854822</v>
-      </c>
-      <c r="T10" s="17" t="s">
-        <v>58</v>
-      </c>
       <c r="U10" s="17" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="V10" s="18">
-        <v>0.01585278673398263</v>
+        <v>0.01587749260351838</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1762,7 +1765,7 @@
         <v>59</v>
       </c>
       <c r="D11" s="10">
-        <v>0.01341746783785012</v>
+        <v>0.013033674301944</v>
       </c>
       <c r="E11" s="11" t="s">
         <v>68</v>
@@ -1771,7 +1774,7 @@
         <v>69</v>
       </c>
       <c r="G11" s="12">
-        <v>0.0134338823191002</v>
+        <v>0.01343994682432912</v>
       </c>
       <c r="H11" s="13" t="s">
         <v>68</v>
@@ -1780,7 +1783,7 @@
         <v>77</v>
       </c>
       <c r="J11" s="14">
-        <v>0.05545381233796821</v>
+        <v>0.0552251898204956</v>
       </c>
       <c r="K11" s="15" t="s">
         <v>83</v>
@@ -1789,7 +1792,7 @@
         <v>84</v>
       </c>
       <c r="M11" s="16">
-        <v>0.01849366354236514</v>
+        <v>0.01851473484102148</v>
       </c>
       <c r="N11" s="17" t="s">
         <v>91</v>
@@ -1798,25 +1801,25 @@
         <v>92</v>
       </c>
       <c r="P11" s="18">
-        <v>0.01324403698046772</v>
+        <v>0.01614850800503837</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="S11" s="16">
-        <v>0.01902183887326397</v>
+        <v>0.01895938650798894</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="V11" s="18">
-        <v>0.01490401316850356</v>
+        <v>0.01492724041624739</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1828,16 +1831,16 @@
         <v>61</v>
       </c>
       <c r="D12" s="10">
-        <v>0.01299781370580032</v>
+        <v>0.01288107075504116</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F12" s="11" t="s">
         <v>70</v>
       </c>
       <c r="G12" s="12">
-        <v>0.01318616972135808</v>
+        <v>0.01316223256356711</v>
       </c>
       <c r="H12" s="13" t="s">
         <v>78</v>
@@ -1846,7 +1849,7 @@
         <v>79</v>
       </c>
       <c r="J12" s="14">
-        <v>0.04415573485299391</v>
+        <v>0.04397369154817261</v>
       </c>
       <c r="K12" s="15" t="s">
         <v>75</v>
@@ -1855,34 +1858,34 @@
         <v>85</v>
       </c>
       <c r="M12" s="16">
-        <v>0.01059609949599814</v>
+        <v>0.01062467767172336</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P12" s="18">
-        <v>0.0126681616781182</v>
+        <v>0.01306484653540416</v>
       </c>
       <c r="Q12" s="15" t="s">
         <v>86</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="S12" s="16">
-        <v>0.01280799670899751</v>
+        <v>0.01278735729772109</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="V12" s="18">
-        <v>0.01283545254154441</v>
+        <v>0.01285545602870696</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1894,7 +1897,7 @@
         <v>63</v>
       </c>
       <c r="D13" s="10">
-        <v>0.01288509652221851</v>
+        <v>0.01284240964210072</v>
       </c>
       <c r="E13" s="11" t="s">
         <v>71</v>
@@ -1903,16 +1906,16 @@
         <v>72</v>
       </c>
       <c r="G13" s="12">
-        <v>0.0131042581765579</v>
+        <v>0.01311017387838892</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I13" s="13" t="s">
         <v>80</v>
       </c>
       <c r="J13" s="14">
-        <v>0.02115636365520308</v>
+        <v>0.02106914113766109</v>
       </c>
       <c r="K13" s="15" t="s">
         <v>86</v>
@@ -1921,34 +1924,34 @@
         <v>87</v>
       </c>
       <c r="M13" s="16">
-        <v>0.01026912050671343</v>
+        <v>0.01028082093073375</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P13" s="18">
-        <v>0.0123204560642378</v>
+        <v>0.01249676276609561</v>
       </c>
       <c r="Q13" s="15" t="s">
         <v>73</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="S13" s="16">
-        <v>0.01082225239595647</v>
+        <v>0.01080481290692378</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="V13" s="18">
-        <v>0.01110803613622016</v>
+        <v>0.01014807765241316</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1959,7 +1962,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -1968,7 +1971,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -1977,7 +1980,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -1986,7 +1989,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -1995,7 +1998,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -2004,7 +2007,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -2013,7 +2016,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -2022,67 +2025,67 @@
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D16" s="10">
-        <v>0.06145316299213483</v>
+        <v>0.0654417346648527</v>
       </c>
       <c r="E16" s="11" t="s">
         <v>64</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G16" s="12">
-        <v>0.08523212689903491</v>
+        <v>0.08527060354092987</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J16" s="14">
-        <v>0.2321622499403485</v>
+        <v>0.2328605002822111</v>
       </c>
       <c r="K16" s="15" t="s">
         <v>68</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="M16" s="16">
-        <v>0.03001868518172112</v>
+        <v>0.02555103866878159</v>
       </c>
       <c r="N16" s="17" t="s">
         <v>78</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P16" s="18">
-        <v>0.05544953044744232</v>
+        <v>0.05469930405845713</v>
       </c>
       <c r="Q16" s="15" t="s">
         <v>68</v>
       </c>
       <c r="R16" s="15" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="S16" s="16">
-        <v>0.0275897543197223</v>
+        <v>0.02737654603186862</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="V16" s="18">
-        <v>0.03006186824295598</v>
+        <v>0.03010871833986794</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -2091,294 +2094,294 @@
         <v>64</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D17" s="10">
-        <v>0.05452823376176097</v>
+        <v>0.0546786755986436</v>
       </c>
       <c r="E17" s="11" t="s">
         <v>66</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G17" s="12">
-        <v>0.04117151840674023</v>
+        <v>0.04175044632685521</v>
       </c>
       <c r="H17" s="13" t="s">
         <v>75</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="J17" s="14">
-        <v>0.05303518887800202</v>
+        <v>0.05281653775403552</v>
       </c>
       <c r="K17" s="15" t="s">
         <v>73</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M17" s="16">
-        <v>0.02501602326831171</v>
+        <v>0.02504452600906252</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P17" s="18">
-        <v>0.04955659775054871</v>
+        <v>0.04888610212902085</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="S17" s="16">
-        <v>0.02279125316959948</v>
+        <v>0.02275452626699637</v>
       </c>
       <c r="T17" s="17" t="s">
         <v>68</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="V17" s="18">
-        <v>0.0295301897073827</v>
+        <v>0.02881169910684581</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D18" s="10">
-        <v>0.02358811503511129</v>
+        <v>0.02365319396963144</v>
       </c>
       <c r="E18" s="11" t="s">
         <v>68</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G18" s="12">
-        <v>0.02392548527008479</v>
+        <v>0.02393628603691289</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="J18" s="14">
-        <v>0.02992047076771132</v>
+        <v>0.03121177937628191</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="M18" s="16">
-        <v>0.02270949709452313</v>
+        <v>0.02273537182694258</v>
       </c>
       <c r="N18" s="17" t="s">
         <v>68</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P18" s="18">
-        <v>0.02741938790685445</v>
+        <v>0.02619516251695594</v>
       </c>
       <c r="Q18" s="15" t="s">
         <v>75</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="S18" s="16">
-        <v>0.02027022096733293</v>
+        <v>0.02023755657517903</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="V18" s="18">
-        <v>0.02344378939515098</v>
+        <v>0.02348032550781935</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D19" s="10">
-        <v>0.02307230644910842</v>
+        <v>0.02313596228249721</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G19" s="12">
-        <v>0.01557438748797483</v>
+        <v>0.01558141828905783</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="J19" s="14">
-        <v>0.01602507126703839</v>
+        <v>0.01599266144160074</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="M19" s="16">
-        <v>0.02153146204605311</v>
+        <v>0.02155599454964499</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P19" s="18">
-        <v>0.01587922947124591</v>
+        <v>0.01566438514542476</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="S19" s="16">
-        <v>0.01643755093119254</v>
+        <v>0.01641106268468889</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="V19" s="18">
-        <v>0.0231494731387993</v>
+        <v>0.02318555057255186</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D20" s="10">
-        <v>0.01919177497131671</v>
+        <v>0.01924472452938121</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G20" s="12">
-        <v>0.01352801447729909</v>
+        <v>0.01339989706434078</v>
       </c>
       <c r="H20" s="13" t="s">
         <v>68</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J20" s="14">
-        <v>0.0106359224244439</v>
+        <v>0.01059207311530172</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M20" s="16">
-        <v>0.01353090718214072</v>
+        <v>0.01445623479786961</v>
       </c>
       <c r="N20" s="17" t="s">
         <v>83</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P20" s="18">
-        <v>0.0150671023173338</v>
+        <v>0.0148740863593691</v>
       </c>
       <c r="Q20" s="15" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="R20" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="S20" s="16">
-        <v>0.01372511582686201</v>
+        <v>0.01370299852649075</v>
       </c>
       <c r="T20" s="17" t="s">
         <v>73</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="V20" s="18">
-        <v>0.01775056484148834</v>
+        <v>0.01777822831457474</v>
       </c>
     </row>
     <row r="23" spans="1:22">
       <c r="B23" s="19" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="24" spans="1:22">
       <c r="B24" s="20" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="25" spans="1:22">
       <c r="B25" s="20" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="26" spans="1:22">
       <c r="B26" s="20" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -2386,7 +2389,7 @@
         <v>75</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -2394,180 +2397,180 @@
         <v>78</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="B30" s="19" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="31" spans="1:22">
       <c r="B31" s="20" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D31" s="22">
-        <v>0.2681438106575063</v>
+        <v>0.2682822532127812</v>
       </c>
     </row>
     <row r="32" spans="1:22">
       <c r="B32" s="20" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D32" s="22">
-        <v>0.2117008545282758</v>
+        <v>0.2111096780100063</v>
       </c>
     </row>
     <row r="33" spans="2:4">
       <c r="B33" s="20" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D33" s="22">
-        <v>0.2068635784688321</v>
+        <v>0.2067125951055939</v>
       </c>
     </row>
     <row r="34" spans="2:4">
       <c r="B34" s="20" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D34" s="22">
-        <v>0.07464260935696003</v>
+        <v>0.07518621080760743</v>
       </c>
     </row>
     <row r="35" spans="2:4">
       <c r="B35" s="20" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D35" s="22">
-        <v>0.06361848853455118</v>
+        <v>0.06311785525660063</v>
       </c>
     </row>
     <row r="36" spans="2:4">
       <c r="B36" s="20" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D36" s="22">
-        <v>0.05503219279953674</v>
+        <v>0.05593221662741933</v>
       </c>
     </row>
     <row r="37" spans="2:4">
       <c r="B37" s="20" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D37" s="22">
-        <v>0.03279392767452909</v>
+        <v>0.03294332337726814</v>
       </c>
     </row>
     <row r="38" spans="2:4">
       <c r="B38" s="20" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D38" s="22">
-        <v>0.0247535498660441</v>
+        <v>0.02457056068907284</v>
       </c>
     </row>
     <row r="39" spans="2:4">
       <c r="B39" s="20" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D39" s="22">
-        <v>0.01807543783373902</v>
+        <v>0.01842781841102016</v>
       </c>
     </row>
     <row r="40" spans="2:4">
       <c r="B40" s="20" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D40" s="22">
-        <v>0.01719751315701725</v>
+        <v>0.01703312295216734</v>
       </c>
     </row>
     <row r="41" spans="2:4">
       <c r="B41" s="20" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D41" s="22">
-        <v>0.01223678054540146</v>
+        <v>0.01262076903525325</v>
       </c>
     </row>
     <row r="42" spans="2:4">
       <c r="B42" s="20" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D42" s="22">
-        <v>0.01105084312857307</v>
+        <v>0.0109220468074348</v>
       </c>
     </row>
     <row r="43" spans="2:4">
       <c r="B43" s="20" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D43" s="22">
-        <v>0.001482935302601378</v>
+        <v>0.001498202981659782</v>
       </c>
     </row>
     <row r="44" spans="2:4">
       <c r="B44" s="20" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D44" s="22">
-        <v>0.001394543050518925</v>
+        <v>0.001336950438805473</v>
       </c>
     </row>
     <row r="45" spans="2:4">
       <c r="B45" s="20" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D45" s="22">
         <v>0.0003063962873093693</v>
@@ -2575,13 +2578,13 @@
     </row>
     <row r="46" spans="2:4">
       <c r="B46" s="20" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D46" s="20" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>
@@ -2960,331 +2963,331 @@
     <row r="9" spans="1:22">
       <c r="A9" s="1"/>
       <c r="B9" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D9" s="10">
-        <v>0.1538502654193637</v>
+        <v>0.1546942234735098</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G9" s="12">
-        <v>0.1840505350201732</v>
+        <v>0.1840045974190681</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="J9" s="14">
-        <v>0.2655881669929213</v>
+        <v>0.264638198259688</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M9" s="16">
-        <v>0.1578426925974449</v>
+        <v>0.1593476898719052</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P9" s="18">
-        <v>0.123011869473703</v>
+        <v>0.1213936313526428</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="S9" s="16">
-        <v>0.1470972930014534</v>
+        <v>0.1467643578311804</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="V9" s="18">
-        <v>0.1094100010036437</v>
+        <v>0.1089238905128201</v>
       </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1"/>
       <c r="B10" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D10" s="10">
-        <v>0.0826876844214421</v>
+        <v>0.08271891725873581</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G10" s="12">
-        <v>0.1393536059276285</v>
+        <v>0.1393652011739311</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J10" s="14">
-        <v>0.08023810938540973</v>
+        <v>0.07990730726754749</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M10" s="16">
-        <v>0.1020796310369193</v>
+        <v>0.1022415321978086</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P10" s="18">
-        <v>0.1196773836118816</v>
+        <v>0.1185949397926938</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="S10" s="16">
-        <v>0.1149337386682617</v>
+        <v>0.1146980912731564</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="V10" s="18">
-        <v>0.1078738934536141</v>
+        <v>0.1052070318529225</v>
       </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1"/>
       <c r="B11" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D11" s="10">
-        <v>0.05869909710104126</v>
+        <v>0.05888958133977201</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G11" s="12">
-        <v>0.07462373293699406</v>
+        <v>0.07384176447037352</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J11" s="14">
-        <v>0.04451975613815871</v>
+        <v>0.04496691723763607</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M11" s="16">
-        <v>0.08936551159039954</v>
+        <v>0.08921221495672947</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P11" s="18">
-        <v>0.08612190142119347</v>
+        <v>0.08516993965812243</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="S11" s="16">
-        <v>0.08916270058204429</v>
+        <v>0.09030062633003694</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="V11" s="18">
-        <v>0.09265822846893949</v>
+        <v>0.09547302673239319</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1"/>
       <c r="B12" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D12" s="10">
-        <v>0.03695333665202506</v>
+        <v>0.03175329441640085</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G12" s="12">
-        <v>0.02379488493002533</v>
+        <v>0.02417891161588913</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="J12" s="14">
-        <v>0.02163713797540297</v>
+        <v>0.02154793334282171</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M12" s="16">
-        <v>0.03758913460057658</v>
+        <v>0.03974576153655089</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P12" s="18">
-        <v>0.03237566015940632</v>
+        <v>0.0441530559831546</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="S12" s="16">
-        <v>0.02879536149144788</v>
+        <v>0.02906049534732991</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="V12" s="18">
-        <v>0.03398707709357816</v>
+        <v>0.03498492412763583</v>
       </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1"/>
       <c r="B13" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D13" s="10">
-        <v>0.02005869469771829</v>
+        <v>0.02021490286659136</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G13" s="12">
-        <v>0.02373753075185056</v>
+        <v>0.02374824666970266</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J13" s="14">
-        <v>0.01661576747734093</v>
+        <v>0.01665933746660311</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="M13" s="16">
-        <v>0.03427431356580436</v>
+        <v>0.03430586827526806</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P13" s="18">
-        <v>0.03084897153528575</v>
+        <v>0.03040074332060953</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="S13" s="16">
-        <v>0.02867058554601775</v>
+        <v>0.02869833769305954</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="V13" s="18">
-        <v>0.03079776348321461</v>
+        <v>0.03081242595031089</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -3295,7 +3298,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -3304,7 +3307,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -3313,7 +3316,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -3322,7 +3325,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -3331,7 +3334,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -3340,7 +3343,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -3349,7 +3352,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -3358,331 +3361,331 @@
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D16" s="10">
-        <v>0.1465537166751869</v>
+        <v>0.1452713048645195</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G16" s="12">
-        <v>0.1588913646341541</v>
+        <v>0.1590328061220095</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="J16" s="14">
-        <v>0.3284940881405419</v>
+        <v>0.3297831905629031</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="M16" s="16">
-        <v>0.1288338780406934</v>
+        <v>0.1253941708249791</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P16" s="18">
-        <v>0.2120746709638698</v>
+        <v>0.2093398363818761</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="R16" s="15" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="S16" s="16">
-        <v>0.1383001876009834</v>
+        <v>0.1379450195657136</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="V16" s="18">
-        <v>0.1557987786801358</v>
+        <v>0.1558472866555431</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D17" s="10">
-        <v>0.1382123426812732</v>
+        <v>0.1383003235301228</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G17" s="12">
-        <v>0.126295698990908</v>
+        <v>0.126622736875535</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J17" s="14">
-        <v>0.1010870644841312</v>
+        <v>0.1018770810585407</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M17" s="16">
-        <v>0.1221930874081625</v>
+        <v>0.1216564969564509</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P17" s="18">
-        <v>0.1279212147368264</v>
+        <v>0.1265575489224343</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="S17" s="16">
-        <v>0.1241570521410879</v>
+        <v>0.1239758501353134</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="V17" s="18">
-        <v>0.1353285868582573</v>
+        <v>0.1358231355023938</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D18" s="10">
-        <v>0.0884056804108919</v>
+        <v>0.08846065578635355</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G18" s="12">
-        <v>0.1025788723013655</v>
+        <v>0.1001105199639274</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="J18" s="14">
-        <v>0.03989170054550869</v>
+        <v>0.03973450698424804</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="M18" s="16">
-        <v>0.08093801723501476</v>
+        <v>0.08102877975806475</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P18" s="18">
-        <v>0.0849122770401164</v>
+        <v>0.08291017883039922</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="S18" s="16">
-        <v>0.1132420405381145</v>
+        <v>0.1130411713954756</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="V18" s="18">
-        <v>0.1182926482765914</v>
+        <v>0.117753540169889</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D19" s="10">
-        <v>0.06210243506528635</v>
+        <v>0.06609279806107822</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G19" s="12">
-        <v>0.02595887779288144</v>
+        <v>0.02601123619230775</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="J19" s="14">
-        <v>0.01778005038027149</v>
+        <v>0.01770674757731985</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M19" s="16">
-        <v>0.05554576668565076</v>
+        <v>0.05557537815422622</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="P19" s="18">
-        <v>0.0307506898922022</v>
+        <v>0.03077097071826938</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="S19" s="16">
-        <v>0.0336144420828797</v>
+        <v>0.03417670135480571</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="V19" s="18">
-        <v>0.04096816726272372</v>
+        <v>0.04103201434604708</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D20" s="10">
-        <v>0.0371526692130853</v>
+        <v>0.0372345969480696</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G20" s="12">
-        <v>0.02366389658362836</v>
+        <v>0.02366074934601088</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="J20" s="14">
-        <v>0.01697361995678191</v>
+        <v>0.0168780779516973</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M20" s="16">
-        <v>0.03423379145819326</v>
+        <v>0.0342814957237212</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P20" s="18">
-        <v>0.02749155511831053</v>
+        <v>0.02711959723232723</v>
       </c>
       <c r="Q20" s="15" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="R20" s="15" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="S20" s="16">
-        <v>0.02654208914750698</v>
+        <v>0.02649931797052301</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="V20" s="18">
-        <v>0.01955017329673217</v>
+        <v>0.01999889779827887</v>
       </c>
     </row>
   </sheetData>
